--- a/Dev_GNC/TableData/Proto/Proto_StagePresetDataTable.xlsx
+++ b/Dev_GNC/TableData/Proto/Proto_StagePresetDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\Proto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45A9AA2-F011-43DE-B13A-99C733AB3B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6698C617-8D08-4D7B-8730-6A942E7138F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{67419AA7-57ED-4FCD-9324-24F0D4544D93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{67419AA7-57ED-4FCD-9324-24F0D4544D93}"/>
   </bookViews>
   <sheets>
     <sheet name="_Schema" sheetId="1" r:id="rId1"/>
@@ -104,7 +104,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>asset:TileMapPreset</t>
+    <t>asset:UTileMapPreset</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
